--- a/4 курс/Metrology/606-22_РечукДМ_Лаб8.xlsx
+++ b/4 курс/Metrology/606-22_РечукДМ_Лаб8.xlsx
@@ -1,25 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9368E3-EF22-42E2-ABB2-639F8893A8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="132">
   <si>
     <t>Шкала оценки качественных характеристик:</t>
   </si>
@@ -382,12 +397,45 @@
   </si>
   <si>
     <t>Общая оценка</t>
+  </si>
+  <si>
+    <t>Метрика</t>
+  </si>
+  <si>
+    <t>Время запуска (с)</t>
+  </si>
+  <si>
+    <t>Открытие файла 10МБ (с)</t>
+  </si>
+  <si>
+    <t>Поиск текста (с)</t>
+  </si>
+  <si>
+    <t>Память (МБ)</t>
+  </si>
+  <si>
+    <t>Частота сбоев</t>
+  </si>
+  <si>
+    <t>Восстановление (с)</t>
+  </si>
+  <si>
+    <t>Сохранение данных (%)</t>
+  </si>
+  <si>
+    <t>Лог-файлы (КБ/день)</t>
+  </si>
+  <si>
+    <t>Характеристика</t>
+  </si>
+  <si>
+    <t>Усредненные качественные характеристики качества</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -434,9 +482,6 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -445,6 +490,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -510,7 +558,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -855,7 +902,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -887,6 +933,1149 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Сравнение характеристик качества</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Notepad++</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$L$3:$L$10</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Время запуска (с)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Открытие файла 10МБ (с)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Поиск текста (с)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Память (МБ)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Частота сбоев</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Восстановление (с)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Сохранение данных (%)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Лог-файлы (КБ/день)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$M$3:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-984E-4503-945D-040C9BEC47CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Блокнот Windows</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$L$3:$L$10</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Время запуска (с)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Открытие файла 10МБ (с)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Поиск текста (с)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Память (МБ)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Частота сбоев</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Восстановление (с)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Сохранение данных (%)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Лог-файлы (КБ/день)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$N$3:$N$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-984E-4503-945D-040C9BEC47CA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="620601599"/>
+        <c:axId val="620603999"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="620601599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Метрики</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="620603999"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="620603999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+                  <a:t>Значение</a:t>
+                </a:r>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="620601599"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Сравнение характеристик качества</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$Z$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Notepad++</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Y$3:$Y$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Производительность</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Надежность</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Сопровождаемость</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Переносимость</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$Z$3:$Z$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-185C-4511-9FEE-B1363D60B5C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист1!$AA$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Блокнот Windows</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист1!$Y$3:$Y$6</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Производительность</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Надежность</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Сопровождаемость</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Переносимость</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$AA$3:$AA$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-185C-4511-9FEE-B1363D60B5C3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="884925487"/>
+        <c:axId val="884918767"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="884925487"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="884918767"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="884918767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="884925487"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -962,6 +2151,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -1433,6 +2702,1014 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1482,7 +3759,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1492,6 +3775,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>250370</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>179613</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{94122ABF-6ABA-D475-774A-AC8361AF194A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>391886</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>457199</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68B7EEF8-913D-B11B-5711-0DAFF7E1821E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1762,1068 +4117,1200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="3" width="71.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.140625" customWidth="1"/>
-    <col min="6" max="6" width="33.85546875" customWidth="1"/>
-    <col min="7" max="7" width="48.28515625" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" customWidth="1"/>
+    <col min="3" max="3" width="71.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" customWidth="1"/>
+    <col min="6" max="6" width="33.88671875" customWidth="1"/>
+    <col min="7" max="7" width="48.33203125" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="12" max="12" width="24.77734375" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" customWidth="1"/>
+    <col min="25" max="25" width="20.6640625" customWidth="1"/>
+    <col min="26" max="26" width="10.44140625" customWidth="1"/>
+    <col min="27" max="27" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="E1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="L2" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="M3" s="5">
+        <v>2</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>75</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="L4" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>80</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="L5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="N5" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>90</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="L6" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="M6" s="5">
+        <v>45</v>
+      </c>
+      <c r="N6" s="5">
+        <v>20</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>50</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="L7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E9" s="2" t="s">
+      <c r="L8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="M8" s="5">
+        <v>3</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="5">
+        <v>95</v>
+      </c>
+      <c r="N9" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="L10" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="M10" s="5">
         <v>50</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="N10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="2" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E13" s="2" t="s">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="F13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E15" s="2" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E15" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="F15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="2" t="s">
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="2" t="s">
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E20" s="1" t="s">
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E21" s="2" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E22" s="2" t="s">
+    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="F22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="2">
+      <c r="H23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="1">
         <v>5</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="2" t="s">
+    <row r="24" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="2">
+      <c r="H24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="1">
         <v>5</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="2" t="s">
+    <row r="25" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="2">
+      <c r="H25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="1">
         <v>5</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E26" s="2" t="s">
+    <row r="26" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E26" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="F26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="2">
+      <c r="H27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="1">
         <v>4</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="2" t="s">
+    <row r="28" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="2">
+      <c r="H28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="1">
         <v>4</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="2" t="s">
+    <row r="29" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="2">
+      <c r="H29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="1">
         <v>5</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="2" t="s">
+    <row r="30" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="2">
+      <c r="H30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="1">
         <v>4</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="2" t="s">
+    <row r="31" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="2">
+      <c r="H31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="1">
         <v>4</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E32" s="2" t="s">
+    <row r="32" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="F32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="2">
+      <c r="H33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="1">
         <v>5</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="2" t="s">
+    <row r="34" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="2">
+      <c r="H34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="1">
         <v>5</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E35" s="2" t="s">
+    <row r="35" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E35" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="F35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="2">
+      <c r="H36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="1">
         <v>4</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="2" t="s">
+    <row r="37" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="2">
+      <c r="H37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I37" s="1">
         <v>4</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E38" s="2" t="s">
+    <row r="38" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="F38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="2" t="s">
+      <c r="G39" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39" s="2">
+      <c r="H39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="1">
         <v>5</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="2" t="s">
+    <row r="40" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="2">
+      <c r="H40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="1">
         <v>4</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="2" t="s">
+    <row r="41" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="2">
+      <c r="H41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="1">
         <v>5</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="2" t="s">
+    <row r="42" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="2">
+      <c r="H42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="1">
         <v>4</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E43" s="2" t="s">
+    <row r="43" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E43" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="44" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="F43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="2">
+      <c r="H44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="1">
         <v>4</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="2" t="s">
+    <row r="45" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="2">
+      <c r="H45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="1">
         <v>4</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F46" s="2" t="s">
+    <row r="46" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46" s="2">
+      <c r="H46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="1">
         <v>5</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="5:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E48" s="7" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
     </row>
-    <row r="49" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E49" s="2" t="s">
+    <row r="49" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E50" s="2" t="s">
+    <row r="50" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="5">
         <f>AVERAGE(I23:I25)</f>
         <v>5</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <f>AVERAGE(J23:J25)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E51" s="2" t="s">
+    <row r="51" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E51" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="5">
         <f>AVERAGE(I27:I31)</f>
         <v>4.2</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <f>AVERAGE(J27:J31)</f>
         <v>4.2</v>
       </c>
     </row>
-    <row r="52" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E52" s="2" t="s">
+    <row r="52" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E52" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="5">
         <f>AVERAGE(I33:I34)</f>
         <v>5</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <f>AVERAGE(J33:J34)</f>
         <v>4.5</v>
       </c>
     </row>
-    <row r="53" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E53" s="2" t="s">
+    <row r="53" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E53" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="5">
         <f>AVERAGE(I36:I37)</f>
         <v>4</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <f>AVERAGE(J36:J37)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E54" s="2" t="s">
+    <row r="54" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E54" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="5">
         <f>AVERAGE(I39:I42)</f>
         <v>4.5</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <f>AVERAGE(J39:J42)</f>
         <v>1.25</v>
       </c>
     </row>
-    <row r="55" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E55" s="2" t="s">
+    <row r="55" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E55" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="5">
         <f>AVERAGE(I44:I46)</f>
         <v>4.333333333333333</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <f>AVERAGE(J44:J46)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E56" s="5" t="s">
+    <row r="56" spans="5:7" x14ac:dyDescent="0.3">
+      <c r="E56" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="5">
         <f>AVERAGE(F50:F55)</f>
         <v>4.5055555555555555</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <f>AVERAGE(G50:G55)</f>
         <v>3.6583333333333332</v>
       </c>
